--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,642 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128340283</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>834875</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7485980</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128339871</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>834497</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7486248</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128339870</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>834875</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7485983</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128339786</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>834250</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7486258</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128340284</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>834490</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7486244</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128339873</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92637</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>834326</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7486374</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>128340283</v>
       </c>
       <c r="B4" t="n">
-        <v>78790</v>
+        <v>78791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>128339871</v>
       </c>
       <c r="B5" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339870</v>
+        <v>128339786</v>
       </c>
       <c r="B6" t="n">
-        <v>78790</v>
+        <v>92650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834875</v>
+        <v>834250</v>
       </c>
       <c r="R6" t="n">
-        <v>7485983</v>
+        <v>7486258</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339786</v>
+        <v>128339870</v>
       </c>
       <c r="B7" t="n">
-        <v>92645</v>
+        <v>78791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834250</v>
+        <v>834875</v>
       </c>
       <c r="R7" t="n">
-        <v>7486258</v>
+        <v>7485983</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1343,7 +1343,7 @@
         <v>128340284</v>
       </c>
       <c r="B8" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128339873</v>
       </c>
       <c r="B9" t="n">
-        <v>92637</v>
+        <v>92642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>128340283</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>128339871</v>
       </c>
       <c r="B5" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339786</v>
+        <v>128339870</v>
       </c>
       <c r="B6" t="n">
-        <v>92650</v>
+        <v>78841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834250</v>
+        <v>834875</v>
       </c>
       <c r="R6" t="n">
-        <v>7486258</v>
+        <v>7485983</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339870</v>
+        <v>128339786</v>
       </c>
       <c r="B7" t="n">
-        <v>78791</v>
+        <v>92742</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834875</v>
+        <v>834250</v>
       </c>
       <c r="R7" t="n">
-        <v>7485983</v>
+        <v>7486258</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1343,7 +1343,7 @@
         <v>128340284</v>
       </c>
       <c r="B8" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128339873</v>
       </c>
       <c r="B9" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339870</v>
+        <v>128339786</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>92742</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834875</v>
+        <v>834250</v>
       </c>
       <c r="R6" t="n">
-        <v>7485983</v>
+        <v>7486258</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339786</v>
+        <v>128339870</v>
       </c>
       <c r="B7" t="n">
-        <v>92742</v>
+        <v>78841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834250</v>
+        <v>834875</v>
       </c>
       <c r="R7" t="n">
-        <v>7486258</v>
+        <v>7485983</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339786</v>
+        <v>128339870</v>
       </c>
       <c r="B6" t="n">
-        <v>92742</v>
+        <v>78841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834250</v>
+        <v>834875</v>
       </c>
       <c r="R6" t="n">
-        <v>7486258</v>
+        <v>7485983</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339870</v>
+        <v>128339786</v>
       </c>
       <c r="B7" t="n">
-        <v>78841</v>
+        <v>92742</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834875</v>
+        <v>834250</v>
       </c>
       <c r="R7" t="n">
-        <v>7485983</v>
+        <v>7486258</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>128340283</v>
       </c>
       <c r="B4" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>128339871</v>
       </c>
       <c r="B5" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128339870</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>128339786</v>
       </c>
       <c r="B7" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>128340284</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128339873</v>
       </c>
       <c r="B9" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339870</v>
+        <v>128339786</v>
       </c>
       <c r="B6" t="n">
-        <v>78845</v>
+        <v>92754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834875</v>
+        <v>834250</v>
       </c>
       <c r="R6" t="n">
-        <v>7485983</v>
+        <v>7486258</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339786</v>
+        <v>128339870</v>
       </c>
       <c r="B7" t="n">
-        <v>92754</v>
+        <v>78845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834250</v>
+        <v>834875</v>
       </c>
       <c r="R7" t="n">
-        <v>7486258</v>
+        <v>7485983</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>128340283</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>128339871</v>
       </c>
       <c r="B5" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128339786</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>128339870</v>
       </c>
       <c r="B7" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>128340284</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128339873</v>
       </c>
       <c r="B9" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339786</v>
+        <v>128339870</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>78847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834250</v>
+        <v>834875</v>
       </c>
       <c r="R6" t="n">
-        <v>7486258</v>
+        <v>7485983</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339870</v>
+        <v>128339786</v>
       </c>
       <c r="B7" t="n">
-        <v>78847</v>
+        <v>92756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834875</v>
+        <v>834250</v>
       </c>
       <c r="R7" t="n">
-        <v>7485983</v>
+        <v>7486258</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -1025,7 +1025,7 @@
         <v>128339871</v>
       </c>
       <c r="B5" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339870</v>
+        <v>128339786</v>
       </c>
       <c r="B6" t="n">
-        <v>78847</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834875</v>
+        <v>834250</v>
       </c>
       <c r="R6" t="n">
-        <v>7485983</v>
+        <v>7486258</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339786</v>
+        <v>128339870</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>78847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834250</v>
+        <v>834875</v>
       </c>
       <c r="R7" t="n">
-        <v>7486258</v>
+        <v>7485983</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1343,7 +1343,7 @@
         <v>128340284</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128339873</v>
       </c>
       <c r="B9" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>128340283</v>
       </c>
       <c r="B4" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>128339871</v>
       </c>
       <c r="B5" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339786</v>
+        <v>128339870</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>78874</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834250</v>
+        <v>834875</v>
       </c>
       <c r="R6" t="n">
-        <v>7486258</v>
+        <v>7485983</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339870</v>
+        <v>128339786</v>
       </c>
       <c r="B7" t="n">
-        <v>78847</v>
+        <v>92784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834875</v>
+        <v>834250</v>
       </c>
       <c r="R7" t="n">
-        <v>7485983</v>
+        <v>7486258</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1343,7 +1343,7 @@
         <v>128340284</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128339873</v>
       </c>
       <c r="B9" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339870</v>
+        <v>128339786</v>
       </c>
       <c r="B6" t="n">
-        <v>78874</v>
+        <v>92784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834875</v>
+        <v>834250</v>
       </c>
       <c r="R6" t="n">
-        <v>7485983</v>
+        <v>7486258</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339786</v>
+        <v>128339870</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>78874</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834250</v>
+        <v>834875</v>
       </c>
       <c r="R7" t="n">
-        <v>7486258</v>
+        <v>7485983</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>128340283</v>
       </c>
       <c r="B4" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>128339871</v>
       </c>
       <c r="B5" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339786</v>
+        <v>128339870</v>
       </c>
       <c r="B6" t="n">
-        <v>92784</v>
+        <v>78878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834250</v>
+        <v>834875</v>
       </c>
       <c r="R6" t="n">
-        <v>7486258</v>
+        <v>7485983</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339870</v>
+        <v>128339786</v>
       </c>
       <c r="B7" t="n">
-        <v>78874</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834875</v>
+        <v>834250</v>
       </c>
       <c r="R7" t="n">
-        <v>7485983</v>
+        <v>7486258</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1343,7 +1343,7 @@
         <v>128340284</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128339873</v>
       </c>
       <c r="B9" t="n">
-        <v>92776</v>
+        <v>92786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339870</v>
+        <v>128339786</v>
       </c>
       <c r="B6" t="n">
-        <v>78878</v>
+        <v>92794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834875</v>
+        <v>834250</v>
       </c>
       <c r="R6" t="n">
-        <v>7485983</v>
+        <v>7486258</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339786</v>
+        <v>128339870</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>78878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834250</v>
+        <v>834875</v>
       </c>
       <c r="R7" t="n">
-        <v>7486258</v>
+        <v>7485983</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>128340283</v>
       </c>
       <c r="B4" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>128339871</v>
       </c>
       <c r="B5" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>128339786</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>128339870</v>
       </c>
       <c r="B7" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>128340284</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128339873</v>
       </c>
       <c r="B9" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>564900</v>
+        <v>128339798</v>
       </c>
       <c r="B2" t="n">
-        <v>90668</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Siikajoki, Nb</t>
+          <t>Anttis, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>834289.2563958452</v>
+        <v>834755</v>
       </c>
       <c r="R2" t="n">
-        <v>7486206.4158021</v>
+        <v>7486086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-08-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-08-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Talhed, smalfotad taggsvamp, tallriska, tallgråticka</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,77 +765,73 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sonja Kuoljok</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126017320</v>
+        <v>564900</v>
       </c>
       <c r="B3" t="n">
-        <v>92527</v>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Anttis, Nb</t>
+          <t>Siikajoki, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>834328</v>
+        <v>834289</v>
       </c>
       <c r="R3" t="n">
-        <v>7486374</v>
+        <v>7486206</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,17 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2007-08-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2007-08-30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Talhed, smalfotad taggsvamp, tallriska, tallgråticka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,26 +876,35 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128340283</v>
+        <v>126017320</v>
       </c>
       <c r="B4" t="n">
-        <v>78882</v>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -955,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>834875</v>
+        <v>834328</v>
       </c>
       <c r="R4" t="n">
-        <v>7485980</v>
+        <v>7486374</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1022,32 +1007,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128339871</v>
+        <v>128339873</v>
       </c>
       <c r="B5" t="n">
-        <v>92798</v>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>834497</v>
+        <v>834326</v>
       </c>
       <c r="R5" t="n">
-        <v>7486248</v>
+        <v>7486374</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,12 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1128,32 +1113,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128339786</v>
+        <v>126017319</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1167,13 +1152,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>834250</v>
+        <v>834387</v>
       </c>
       <c r="R6" t="n">
-        <v>7486258</v>
+        <v>7486312</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1182,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1234,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128339870</v>
+        <v>128339796</v>
       </c>
       <c r="B7" t="n">
-        <v>78882</v>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,26 +1230,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1273,13 +1258,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>834875</v>
+        <v>834743</v>
       </c>
       <c r="R7" t="n">
-        <v>7485983</v>
+        <v>7486077</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,12 +1288,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1340,32 +1325,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340284</v>
+        <v>128339797</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1379,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>834490</v>
+        <v>834797</v>
       </c>
       <c r="R8" t="n">
-        <v>7486244</v>
+        <v>7486073</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,12 +1394,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1446,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128339873</v>
+        <v>128339872</v>
       </c>
       <c r="B9" t="n">
-        <v>92790</v>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1457,21 +1442,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1485,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>834326</v>
+        <v>834388</v>
       </c>
       <c r="R9" t="n">
-        <v>7486374</v>
+        <v>7486310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,6 +1534,748 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128339786</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>834250</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7486258</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128339790</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>834850</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7486038</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128339871</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>834497</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7486248</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128340284</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>834490</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7486244</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128339870</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>834875</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7485983</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128340263</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>834097</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7485963</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128340283</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Anttis, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>834875</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7485980</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41787-2025 artfynd.xlsx
+++ b/artfynd/A 41787-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339798</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/564900</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017320</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339873</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017319</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339796</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339797</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339872</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339786</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1746,6 +1796,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339790</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1852,6 +1907,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339871</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1958,6 +2018,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340284</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2064,6 +2129,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128339870</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340263</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2276,8 +2351,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340283</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>